--- a/docs/publications/form-990-part-ix.xlsx
+++ b/docs/publications/form-990-part-ix.xlsx
@@ -486,7 +486,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 05:28 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 13:02 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 05:28 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 13:02 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/publications/form-990-part-ix.xlsx
+++ b/docs/publications/form-990-part-ix.xlsx
@@ -486,7 +486,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 13:02 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 13:25 UTC</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 13:02 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 13:25 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/publications/form-990-part-ix.xlsx
+++ b/docs/publications/form-990-part-ix.xlsx
@@ -37,10 +37,10 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,17 +68,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,8 +84,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -457,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -467,6 +464,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,330 +484,368 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 13:25 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NOT CERTIFIED — nobody has put their name to the rate these figures rest on.</t>
+          <t>REHEARSAL — NOT CERTIFIED. A drive produced this signature to prove the mechanism; no person gave it.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>A rate stands and nobody has put their name to it. Nothing here is blocked by that: this is a working document, and it says so rather than waiting.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Nothing resting on it may be sent to a sponsor. The rate itself is arithmetic and stands; what is missing is somebody putting their name to it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Natural category</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Lines</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Management and general</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Fundraising</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Not yet classified</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>5129 Payroll Expenses</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>364</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>5236.7</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="n">
+      <c r="C9" s="6" t="n">
+        <v>1828043.29</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>321089.38</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>47881.57</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>2197014.24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Grant Expenses</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="5" t="n">
         <v>288</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="6" t="n">
         <v>1435160.7</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="n">
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>1435160.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Program Expenses</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="5" t="n">
         <v>704</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>952771.5699999999</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>952771.5699999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Management &amp; Administrative Expenses</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="5" t="n">
         <v>2229</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>647496.23</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>287883.21</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="n">
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>935379.4399999999</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>5010 Depreciation Expense</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>850382.89</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="n">
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>850382.89</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>5080 Fundraising</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="5" t="n">
         <v>345</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>281203.71</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="n">
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>306203.71</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>5310 Interest Expense</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="C15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>49000.78</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>49000.78</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>5001 Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>37261</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" t="n">
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>37261</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>5400 Bad Debt Expense</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
+      <c r="C17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>12037.85</v>
       </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="n">
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>12037.85</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Channel selling fees</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>3923072.39</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>379158.54</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>281203.71</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="9" t="n">
+      <c r="C19" s="8" t="n">
+        <v>5751115.68</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>695011.22</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>329085.28</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>6775212.18</v>
       </c>
     </row>
@@ -824,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -853,228 +889,259 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 13:25 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Supports</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Bytes</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SHA-256</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2025_Balance-Sheet_QuickBooks.xlsx</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>balance-sheet</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="n">
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>46277.95131774604</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>12694</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>09945044139125f6b9de23b577440c2787506bc3c2d55d41c8089d191d4cdfd0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2025-11-17_EDA_Closeout-Letter_06-79-06300.pdf</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>closeout-letter</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>46277.95133289786</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>268795</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>1af898e4f3b71fb740ce31ff7653125a2d5d1e229962a920e2c4fb5a60d040a7</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2025_General-Ledger_QuickBooks.xlsx</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>general-ledger</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>46277.95131755581</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>919460</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>79b67bfda1c982b9d9e69b324771a481ac339f95a0050d6d304878652c2187cc</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2025_Grant-Reconciliation-Workbook_controller.xlsx</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>grant-reconciliation-workbook</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="n">
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>46277.95131785845</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>351351</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>1ee1472a712880c54816870e4b4a7b1e5b520134ffde163f0313ca7908fe7bdf</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>YBI_floorspace_request_9.15.26.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>information-request</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>46280.72173109135</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Heidi Ruby</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>22663</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>224fc92fe21b8a4f05f24069226b7bb240960a6a6b6fabd41fdbc713e7e367c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2025_YBI_Lease-Schedule.xlsx</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>lease-schedule</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10" t="n">
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>46277.95134645429</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>13819</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>b3e05669a68f7cfd73a0f1afa2e09545effaea027647f909c426598e925f810e</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2025_Profit-and-Loss_QuickBooks.xlsx</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>profit-and-loss</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10" t="n">
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>46277.95131765626</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>14806</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>8be4dad4402d014f94b0ef36ded50785a3137cc32134d0724fc474b565dbcb2d</t>
         </is>
